--- a/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0001T0006Z000C1N6_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0001T0006Z000C1N6_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>50.52005590758509</v>
+        <v>8.209509084982578</v>
       </c>
       <c r="D2" t="n">
-        <v>51.37504566801901</v>
+        <v>8.34844492105309</v>
       </c>
       <c r="E2" t="n">
-        <v>15.32748495795664</v>
+        <v>2.490716305667954</v>
       </c>
       <c r="F2" t="n">
-        <v>15.20367798882153</v>
+        <v>2.470597673183498</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>46.64183114909412</v>
+        <v>7.579297561727795</v>
       </c>
       <c r="D3" t="n">
-        <v>47.35583308421663</v>
+        <v>7.695322876185203</v>
       </c>
       <c r="E3" t="n">
-        <v>15.32748495795664</v>
+        <v>2.490716305667954</v>
       </c>
       <c r="F3" t="n">
-        <v>15.20367798882153</v>
+        <v>2.470597673183498</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>70.06914566532559</v>
+        <v>11.38623617061541</v>
       </c>
       <c r="D4" t="n">
-        <v>70.71222402731074</v>
+        <v>11.490736404438</v>
       </c>
       <c r="E4" t="n">
-        <v>15.32748495795664</v>
+        <v>2.490716305667954</v>
       </c>
       <c r="F4" t="n">
-        <v>15.20367798882153</v>
+        <v>2.470597673183498</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>70.05049616574671</v>
+        <v>11.38320562693384</v>
       </c>
       <c r="D5" t="n">
-        <v>70.1167233753109</v>
+        <v>11.39396754848802</v>
       </c>
       <c r="E5" t="n">
-        <v>15.32748495795664</v>
+        <v>2.490716305667954</v>
       </c>
       <c r="F5" t="n">
-        <v>15.20367798882153</v>
+        <v>2.470597673183498</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>60.47795921841062</v>
+        <v>9.827668372991726</v>
       </c>
       <c r="D6" t="n">
-        <v>60.50267357095983</v>
+        <v>9.831684455280973</v>
       </c>
       <c r="E6" t="n">
-        <v>15.32748495795664</v>
+        <v>2.490716305667954</v>
       </c>
       <c r="F6" t="n">
-        <v>15.20367798882153</v>
+        <v>2.470597673183498</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>78.49557286563424</v>
+        <v>12.75553059066556</v>
       </c>
       <c r="D7" t="n">
-        <v>78.45089351949767</v>
+        <v>12.74827019691837</v>
       </c>
       <c r="E7" t="n">
-        <v>15.32748495795664</v>
+        <v>2.490716305667954</v>
       </c>
       <c r="F7" t="n">
-        <v>15.20367798882153</v>
+        <v>2.470597673183498</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>61.58159368433238</v>
+        <v>10.00700897370401</v>
       </c>
       <c r="D8" t="n">
-        <v>62.00437709909037</v>
+        <v>10.07571127860218</v>
       </c>
       <c r="E8" t="n">
-        <v>15.32748495795664</v>
+        <v>2.490716305667954</v>
       </c>
       <c r="F8" t="n">
-        <v>15.20367798882153</v>
+        <v>2.470597673183498</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>8.383107606368375</v>
+        <v>1.362254986034861</v>
       </c>
       <c r="D9" t="n">
-        <v>8.806660034560963</v>
+        <v>1.431082255616156</v>
       </c>
       <c r="E9" t="n">
-        <v>15.32748495795664</v>
+        <v>2.490716305667954</v>
       </c>
       <c r="F9" t="n">
-        <v>15.20367798882153</v>
+        <v>2.470597673183498</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>73.42909704686924</v>
+        <v>11.93222827011625</v>
       </c>
       <c r="D10" t="n">
-        <v>73.2423330189512</v>
+        <v>11.90187911557957</v>
       </c>
       <c r="E10" t="n">
-        <v>15.32748495795664</v>
+        <v>2.490716305667954</v>
       </c>
       <c r="F10" t="n">
-        <v>15.20367798882153</v>
+        <v>2.470597673183498</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>68.42559391738003</v>
+        <v>11.11915901157425</v>
       </c>
       <c r="D11" t="n">
-        <v>68.62011651871383</v>
+        <v>11.150768934291</v>
       </c>
       <c r="E11" t="n">
-        <v>15.32748495795664</v>
+        <v>2.490716305667954</v>
       </c>
       <c r="F11" t="n">
-        <v>15.20367798882153</v>
+        <v>2.470597673183498</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>74.91356480834339</v>
+        <v>12.1734542813558</v>
       </c>
       <c r="D12" t="n">
-        <v>74.55560593006091</v>
+        <v>12.1152859636349</v>
       </c>
       <c r="E12" t="n">
-        <v>15.32748495795664</v>
+        <v>2.490716305667954</v>
       </c>
       <c r="F12" t="n">
-        <v>15.20367798882153</v>
+        <v>2.470597673183498</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>67.64129593601575</v>
+        <v>10.99171058960256</v>
       </c>
       <c r="D13" t="n">
-        <v>67.15468054457125</v>
+        <v>10.91263558849283</v>
       </c>
       <c r="E13" t="n">
-        <v>15.32748495795664</v>
+        <v>2.490716305667954</v>
       </c>
       <c r="F13" t="n">
-        <v>15.20367798882153</v>
+        <v>2.470597673183498</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>59.32236309529713</v>
+        <v>9.639884002985784</v>
       </c>
       <c r="D14" t="n">
-        <v>58.79940861125161</v>
+        <v>9.554903899328387</v>
       </c>
       <c r="E14" t="n">
-        <v>15.32748495795664</v>
+        <v>2.490716305667954</v>
       </c>
       <c r="F14" t="n">
-        <v>15.20367798882153</v>
+        <v>2.470597673183498</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>65.50025002590384</v>
+        <v>10.64379062920937</v>
       </c>
       <c r="D15" t="n">
-        <v>64.90170458039597</v>
+        <v>10.54652699431435</v>
       </c>
       <c r="E15" t="n">
-        <v>15.32748495795664</v>
+        <v>2.490716305667954</v>
       </c>
       <c r="F15" t="n">
-        <v>15.20367798882153</v>
+        <v>2.470597673183498</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>58.15422804698378</v>
+        <v>9.450062057634865</v>
       </c>
       <c r="D16" t="n">
-        <v>57.75560258349621</v>
+        <v>9.385285419818135</v>
       </c>
       <c r="E16" t="n">
-        <v>15.32748495795664</v>
+        <v>2.490716305667954</v>
       </c>
       <c r="F16" t="n">
-        <v>15.20367798882153</v>
+        <v>2.470597673183498</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>50.19852065731813</v>
+        <v>8.157259606814197</v>
       </c>
       <c r="D17" t="n">
-        <v>49.37977870710574</v>
+        <v>8.024214039904683</v>
       </c>
       <c r="E17" t="n">
-        <v>15.32748495795664</v>
+        <v>2.490716305667954</v>
       </c>
       <c r="F17" t="n">
-        <v>15.20367798882153</v>
+        <v>2.470597673183498</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>53.74137686091737</v>
+        <v>8.732973739899073</v>
       </c>
       <c r="D18" t="n">
-        <v>52.86031945924826</v>
+        <v>8.589801912127843</v>
       </c>
       <c r="E18" t="n">
-        <v>15.32748495795664</v>
+        <v>2.490716305667954</v>
       </c>
       <c r="F18" t="n">
-        <v>15.20367798882153</v>
+        <v>2.470597673183498</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>81.58739890739683</v>
+        <v>13.25795232245199</v>
       </c>
       <c r="D19" t="n">
-        <v>81.25713909291487</v>
+        <v>13.20428510259867</v>
       </c>
       <c r="E19" t="n">
-        <v>15.32748495795664</v>
+        <v>2.490716305667954</v>
       </c>
       <c r="F19" t="n">
-        <v>15.20367798882153</v>
+        <v>2.470597673183498</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>60.02603299050873</v>
+        <v>9.754230360957669</v>
       </c>
       <c r="D20" t="n">
-        <v>59.365715347509</v>
+        <v>9.646928743970212</v>
       </c>
       <c r="E20" t="n">
-        <v>15.32748495795664</v>
+        <v>2.490716305667954</v>
       </c>
       <c r="F20" t="n">
-        <v>15.20367798882153</v>
+        <v>2.470597673183498</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>69.63006811893064</v>
+        <v>11.31488606932623</v>
       </c>
       <c r="D21" t="n">
-        <v>69.02048783071973</v>
+        <v>11.21582927249196</v>
       </c>
       <c r="E21" t="n">
-        <v>15.32748495795664</v>
+        <v>2.490716305667954</v>
       </c>
       <c r="F21" t="n">
-        <v>15.20367798882153</v>
+        <v>2.470597673183498</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
